--- a/Requisitos Funcionales (RF)/Requisitos Funcionales (RF) v 0.9/RF01_Activos_Equipos_v0.9.xlsx
+++ b/Requisitos Funcionales (RF)/Requisitos Funcionales (RF) v 0.9/RF01_Activos_Equipos_v0.9.xlsx
@@ -571,20 +571,19 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Permitir el registro, edición, eliminación (con restricciones), consulta y gestión de la información detallada de los equipos médicos. Esto incluye identificación única, datos técnicos, estado operativo, ubicación, información del proveedor (FK), fechas clave de garantía y notas relevantes. Se debe permitir adjuntar documentos e imágenes al equipo. El campo `condicion_origen` permite valores como "Compra", "Donación", "Préstamo", "Demostración", "Evaluación", "Leasing", "Renta", "Comodato", "Otro". VERSIÓN UNIVERSAL (sin contexto Bolivia).</t>
+          <t>Permitir el registro, edición, eliminación (con restricciones), consulta y gestión de la información detallada de los equipos médicos. VERSIÓN UNIVERSAL (sin contexto Bolivia).</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>- Registro de Nuevo Equipo
-- Consulta de Equipos (con filtros: ubicación, estado, condición origen)
-- Edición de Información (campos modelo/marca/numero_serie NO modificables después de creado)
-- Eliminación de Equipo (con restricciones: verificar OTs, documentos, MP, historial, contratos)
-- Asociación de Documentos
-- Subida y Visualización de Imágenes
+- Consulta con filtros (ubicación, estado, condición origen)
+- Edición (modelo/marca/numero_serie NO modificables después de creado)
+- Eliminación con restricciones
+- Asociación de Documentos e Imágenes
 - Asociación de Proveedor (FK con opción "Crear nuevo")
-- Asociación de Contratos (RF12, N:M vía ContratoEquipo)
-- Búsqueda avanzada (nombre/marca/modelo + numero_serie/numero_material)</t>
+- Asociación de Contratos (RF12, N:M)
+- Búsqueda avanzada</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -599,18 +598,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>- RF02 (OTs): los equipos son base para crear OTs
-- RF03 (MP): las tareas MP se definen para equipos específicos
-- RF04 (Repuestos): los equipos pueden tener repuestos asociados vía OTs
-- RF05 (Historial): el historial se genera a partir de eventos relacionados con equipos
-- RF06 (Reportes): reportes por equipo o grupo de equipos
-- RF10 (Proveedores): `proveedor_principal_id` es FK a `Proveedores.id`
-- RF12 (Contratos): relación N:M vía `ContratoEquipo`</t>
+          <t>- RF02 (OTs), RF03 (MP), RF04 (Repuestos), RF05 (Historial), RF06 (Reportes), RF10 (Proveedores), RF12 (Contratos)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Actualizar RF01 permite una gestión más precisa y detallada de los activos del hospital, incluyendo información clave como fechas de garantía y la condición de origen del equipo. La integración con RF10 (proveedores) centraliza la información de contacto y relación comercial. La exclusión de `registro_sanitario_bolivia` (universalidad), `calibracion_proxima` (gestionada vía MP/OT unificado) y `responsable_tecnico_id` (asignación flexible en OT/MP) simplifica el núcleo del sistema. La restricción de eliminación mejora la integridad de los datos.</t>
+          <t>Gestión más precisa de activos, integración con RF10, exclusión de campos obsoletos por universalidad.</t>
         </is>
       </c>
     </row>
@@ -656,17 +649,17 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Obligatorio (NOT NULL)</t>
+          <t>Obligatorio</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Valor Predeterminado</t>
+          <t>Default</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Editable después de creado</t>
+          <t>Editable después</t>
         </is>
       </c>
       <c r="G1" s="3" t="inlineStr">
@@ -711,7 +704,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Identificador único interno del sistema.</t>
+          <t>Identificador único interno.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -756,7 +749,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Actualizar: cambiar a NOT NULL</t>
+          <t>Actualizar: NOT NULL</t>
         </is>
       </c>
     </row>
@@ -796,7 +789,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Mantener (agregar restricción no editable)</t>
+          <t>Mantener + restricción no editable</t>
         </is>
       </c>
     </row>
@@ -831,12 +824,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Número de serie único del fabricante.</t>
+          <t>Número de serie único.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Mantener (agregar restricción no editable)</t>
+          <t>Mantener + restricción no editable</t>
         </is>
       </c>
     </row>
@@ -871,7 +864,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Número de material del fabricante para identificar variantes.</t>
+          <t>Número de material del fabricante.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -916,7 +909,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Mantener (agregar restricción no editable)</t>
+          <t>Mantener + restricción no editable</t>
         </is>
       </c>
     </row>
@@ -951,12 +944,12 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Fecha de compra/adquisición del equipo.</t>
+          <t>Fecha de compra/adquisición.</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Actualizar: cambiar a opcional</t>
+          <t>Actualizar: opcional</t>
         </is>
       </c>
     </row>
@@ -991,7 +984,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Ubicación física actual del equipo.</t>
+          <t>Ubicación física actual.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1031,7 +1024,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Descripción técnica del equipo (¿qué es? ¿qué hace?).</t>
+          <t>Descripción técnica (¿qué es?).</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1071,7 +1064,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>ID del estado operativo del equipo (FK a `Estados_Equipo.id`).</t>
+          <t>FK a Estados_Equipo.id.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1111,7 +1104,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Ruta relativa donde se almacena localmente una imagen del equipo.</t>
+          <t>Ruta relativa de la imagen.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1151,12 +1144,12 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Notas operativas / estado actual / advertencias / accesorios (¿cómo está?).</t>
+          <t>Notas operativas (¿cómo está?).</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>AÑADIR (nuevo campo)</t>
+          <t>AÑADIR (nuevo)</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1184,12 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Fecha de inicio de la garantía (entrega o instalación, lo que ocurra primero).</t>
+          <t>Fecha de inicio de garantía.</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>AÑADIR (nuevo campo)</t>
+          <t>AÑADIR (nuevo)</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1224,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Fecha de fin de la garantía.</t>
+          <t>Fecha de fin de garantía.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1271,12 +1264,12 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Condición bajo la cual se obtuvo el equipo. Dropdown estricto (ver hoja "Valores_Enum_Condicion_Origen").</t>
+          <t>Condición de origen. Dropdown estricto (9 valores).</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>AÑADIR (nuevo campo)</t>
+          <t>AÑADIR (nuevo)</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1304,12 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>ID del proveedor principal del equipo (FK a `Proveedores.id`). Dropdown con opción "Crear nuevo".</t>
+          <t>FK a Proveedores.id. Dropdown con "Crear nuevo".</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>AÑADIR (reemplaza proveedor_principal texto)</t>
+          <t>AÑADIR (reemplaza texto)</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1344,7 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Nombre del proveedor en texto libre (DEPRECATED).</t>
+          <t>Nombre del proveedor en texto libre.</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
@@ -1391,12 +1384,12 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Número de registro sanitario boliviano.</t>
+          <t>Registro sanitario boliviano.</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>ELIMINAR (universalidad, sin contexto Bolivia)</t>
+          <t>ELIMINAR (universalidad)</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1424,12 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Fecha de la próxima calibración programada.</t>
+          <t>Fecha de próxima calibración.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>ELIMINAR (gestionado vía MP/OT unificado)</t>
+          <t>ELIMINAR (vía MP/OT)</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1464,12 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>ID del responsable técnico del equipo (FK a `Usuarios.id`).</t>
+          <t>FK a Usuarios.id.</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>ELIMINAR (asignación flexible en OT/MP)</t>
+          <t>ELIMINAR (asignación en OT/MP)</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1766,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>Universalidad (sin contexto Bolivia). Las normativas específicas se manejarán en versiones posteriores.</t>
+          <t>Universalidad (sin contexto Bolivia)</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1793,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Se gestionará vía Mantenimiento Preventivo (MP) y OT unificadas (en análisis). La calibración periódica será parte del plan unificado.</t>
+          <t>Se gestiona vía MP/OT unificadas</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1820,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>La asignación de técnicos se hace en OT/MP (flexible, no atado al equipo). El administrador asigna personal a las acciones según necesidad.</t>
+          <t>Asignación flexible en OT/MP</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1847,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Reemplazado por FK `proveedor_principal_id` que referencia a `Proveedores.id`. Centraliza la información del proveedor.</t>
+          <t>Reemplazado por FK proveedor_principal_id</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1874,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Notas operativas / estado actual / advertencias / accesorios. Diferenciado de `descripcion` (técnica).</t>
+          <t>Notas operativas (¿cómo está?)</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1901,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Fecha de inicio de la garantía. Puede ser fecha de entrega o instalación, lo que ocurra primero según condiciones del proveedor.</t>
+          <t>Fecha de inicio de garantía</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1923,12 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>TEXT (enum) opcional</t>
+          <t>TEXT (enum)</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Dropdown estricto con 9 valores: Compra, Donación, Préstamo, Demostración, Evaluación, Leasing, Renta, Comodato, Otro.</t>
+          <t>Dropdown estricto 9 valores</t>
         </is>
       </c>
     </row>
@@ -1957,19 +1950,19 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>INTEGER FK opcional</t>
+          <t>INTEGER FK</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>FK a `Proveedores.id`. Dropdown con opción "Crear nuevo" si el proveedor no existe en la BD.</t>
+          <t>FK a Proveedores.id</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Cambio de obligatoriedad</t>
+          <t>Cambio obligatoriedad</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1989,14 +1982,14 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Es el identificador visible del equipo, debe estar siempre.</t>
+          <t>Identificador visible del equipo</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Cambio de obligatoriedad</t>
+          <t>Cambio obligatoriedad</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -2016,7 +2009,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Puede no conocerse la fecha exacta (donaciones, comodatos, etc.).</t>
+          <t>Puede no conocerse (donaciones, etc.)</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2036,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Evita inconsistencias en carpetas (E0001_Modelo_Serie) y .meta.json. Advertencia ROJA en formularios.</t>
+          <t>Evita inconsistencias en carpetas y .meta.json</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2063,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Rechazar eliminación si tiene OTs, documentos, MP, historial o contratos asociados. Mensaje claro con conteos.</t>
+          <t>Rechazar si tiene OTs, documentos, MP, historial, contratos</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2090,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Agregado a EquiposView para filtrar por condición de origen.</t>
+          <t>Agregado a EquiposView</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2117,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Campo eliminado, filtro ya no aplica.</t>
+          <t>Campo eliminado</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2129,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>fecha_inicio_garantia vs fecha_fin_garantia</t>
+          <t>fecha_inicio vs fecha_fin garantia</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2151,7 +2144,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Si ambas fechas están seteadas, inicio debe ser menor o igual a fin.</t>
+          <t>Si ambas fechas están seteadas</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2171,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>🟢 En garantía / 🔴 Vencida / ⚪ Sin garantía. Sin auto-cambio de estado del equipo.</t>
+          <t>En garantía / Vencida / Sin garantía</t>
         </is>
       </c>
     </row>
@@ -2246,12 +2239,12 @@
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Rediseñar el sistema de estados para tener dimensiones independientes: operativo (Operativo/En Mantenimiento/...), ubicación (En Almacén/En Préstamo/...), garantía (derivado), calibración (derivado de MP), crítico (bool).</t>
+          <t>Rediseñar estados: operativo, ubicación, garantía (derivado), calibración (derivado), crítico (bool).</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>Permite filtrado más flexible. No mezcla dimensiones. Ej: un equipo puede estar Operativo + En Préstamo + Garantía Vigente. Costo: rediseño grande, migración, afecta formularios y reportes.</t>
+          <t>Filtrao más flexible. No mezcla dimensiones.</t>
         </is>
       </c>
     </row>
@@ -2271,12 +2264,12 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Flujo "Editar campos bloqueados" con doble confirmación que actualice también nombre de carpeta (E0001_Modelo_Serie) y .meta.json del equipo.</t>
+          <t>Flujo "Editar campos bloqueados" con doble confirmación que actualice carpetas y .meta.json.</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>Para corregir errores de tipeo en modelo/marca/numero_serie sin perder la estructura de archivos. No crítico para v0.9.</t>
+          <t>Para corregir errores de tipeo.</t>
         </is>
       </c>
     </row>
@@ -2296,12 +2289,12 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Versiones diferenciadas: cliente final Bolivia (DIMUTES), importador/proveedor Bolivia, fabricante.</t>
+          <t>Versiones diferenciadas: cliente final Bolivia, importador, fabricante.</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>Cada versión agrega campos y reportes específicos de su normativa. La base universal (v0.9-v1.0) es el común.</t>
+          <t>Cada versión agrega campos y reportes específicos.</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2314,12 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Opción configurable: si la garantía vence, cambiar automáticamente el estado del equipo a "Garantía Vencida".</t>
+          <t>Si la garantía vence, cambiar estado automáticamente.</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>Por defecto desactivado (puede romper flujos manuales). Si se activa, requiere estado "Garantía Vencida" en catálogo.</t>
+          <t>Por defecto desactivado.</t>
         </is>
       </c>
     </row>
@@ -2346,12 +2339,12 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>En el dashboard, mostrar "X equipos con garantía por vencer en los próximos 30/60/90 días".</t>
+          <t>Dashboard: "X equipos con garantía por vencer en 30/60/90 días".</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Útil para planificación financiera. Fácil de implementar una vez que los campos de garantía existan.</t>
+          <t>Útil para planificación financiera.</t>
         </is>
       </c>
     </row>
